--- a/Metatag/OccO_Meta_Tag.xlsx
+++ b/Metatag/OccO_Meta_Tag.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t xml:space="preserve">Ontology Subset </t>
   </si>
@@ -68,6 +68,14 @@
 food or beverage serving worker; 
 </t>
   </si>
+  <si>
+    <t xml:space="preserve">Food service skill or ability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   quality control analysis;
+reading comprehension;
+Problem sensitivity</t>
+  </si>
 </sst>
 </file>
 
@@ -76,11 +84,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -101,12 +110,35 @@
       <sz val="10"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <name val="Annapurna SIL"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Annapurna SIL"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Annapurna SIL"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -196,37 +228,53 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -412,7 +460,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.18"/>
@@ -420,75 +468,86 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="12.02"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="106.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="42.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
